--- a/cet4/result/14_职场女王_从实习生到总裁/14_职场女王_从实习生到总裁_学习版.xlsx
+++ b/cet4/result/14_职场女王_从实习生到总裁/14_职场女王_从实习生到总裁_学习版.xlsx
@@ -399,724 +399,724 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>sun</v>
       </c>
       <c r="B2" t="str">
-        <v>sun</v>
+        <v>/sʌn/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D2" t="str">
         <v>太阳</v>
       </c>
-      <c r="D2" t="str">
-        <v>sun(太阳)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>award</v>
       </c>
       <c r="B3" t="str">
-        <v>award</v>
+        <v>/əˈwɔːrd/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D3" t="str">
         <v>奖品</v>
       </c>
-      <c r="D3" t="str">
-        <v>award(奖品)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>brow</v>
       </c>
       <c r="B4" t="str">
-        <v>brow</v>
+        <v>/braʊ/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>眉毛</v>
       </c>
-      <c r="D4" t="str">
-        <v>brow(眉毛)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>genuine</v>
       </c>
       <c r="B5" t="str">
-        <v>genuine</v>
+        <v>/ˈdʒenjuɪn/</v>
       </c>
       <c r="C5" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>真实的</v>
       </c>
-      <c r="D5" t="str">
-        <v>genuine(真实的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>realize</v>
       </c>
       <c r="B6" t="str">
-        <v>realize</v>
+        <v>/ˈriːəlaɪz/</v>
       </c>
       <c r="C6" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D6" t="str">
         <v>认识到</v>
       </c>
-      <c r="D6" t="str">
-        <v>realize(认识到)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>utter</v>
       </c>
       <c r="B7" t="str">
-        <v>utter</v>
+        <v>/ˈʌtər/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>完全的</v>
       </c>
-      <c r="D7" t="str">
-        <v>utter(完全的)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>neither</v>
       </c>
       <c r="B8" t="str">
-        <v>neither</v>
+        <v>/ˈniːðər,ˈnaɪðər/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v./adj./adv./pron./conj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>两者都不</v>
       </c>
-      <c r="D8" t="str">
-        <v>neither(两者都不)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>textbook</v>
       </c>
       <c r="B9" t="str">
-        <v>textbook</v>
+        <v>/ˈtekstbʊk/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>教科书</v>
       </c>
-      <c r="D9" t="str">
-        <v>textbook(教科书)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>immigrant</v>
       </c>
       <c r="B10" t="str">
-        <v>immigrant</v>
+        <v>/ˈɪmɪɡrənt/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>移民</v>
       </c>
-      <c r="D10" t="str">
-        <v>immigrant(移民)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>teacher</v>
       </c>
       <c r="B11" t="str">
-        <v>teacher</v>
+        <v>/ˈtiːtʃər/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>教师</v>
       </c>
-      <c r="D11" t="str">
-        <v>teacher(教师)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>fight</v>
       </c>
       <c r="B12" t="str">
-        <v>fight</v>
+        <v>/faɪt/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>战斗</v>
       </c>
-      <c r="D12" t="str">
-        <v>fight(战斗)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>enclose</v>
       </c>
       <c r="B13" t="str">
-        <v>enclose</v>
+        <v>/ɪnˈkloʊz/</v>
       </c>
       <c r="C13" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D13" t="str">
         <v>围绕</v>
       </c>
-      <c r="D13" t="str">
-        <v>enclose(围绕)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>inspection</v>
       </c>
       <c r="B14" t="str">
-        <v>inspection</v>
+        <v>/ɪnˈspekʃn/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>视察</v>
       </c>
-      <c r="D14" t="str">
-        <v>inspection(视察)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>sickness</v>
       </c>
       <c r="B15" t="str">
-        <v>sickness</v>
+        <v>/ˈsɪknəs/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>疾病</v>
       </c>
-      <c r="D15" t="str">
-        <v>sickness(疾病)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>matter</v>
       </c>
       <c r="B16" t="str">
-        <v>matter</v>
+        <v>/ˈmætər/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D16" t="str">
         <v>事件</v>
       </c>
-      <c r="D16" t="str">
-        <v>matter(事件)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>bold</v>
       </c>
       <c r="B17" t="str">
-        <v>bold</v>
+        <v>/boʊld/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>大胆的</v>
       </c>
-      <c r="D17" t="str">
-        <v>bold(大胆的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>sort</v>
       </c>
       <c r="B18" t="str">
-        <v>sort</v>
+        <v>/sɔːrt/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>种类</v>
       </c>
-      <c r="D18" t="str">
-        <v>sort(种类)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>multiple</v>
       </c>
       <c r="B19" t="str">
-        <v>multiple</v>
+        <v>/ˈmʌltɪpl/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>多重的</v>
       </c>
-      <c r="D19" t="str">
-        <v>multiple(多重的)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>storage</v>
       </c>
       <c r="B20" t="str">
-        <v>storage</v>
+        <v>/ˈstɔːrɪdʒ/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>存储</v>
       </c>
-      <c r="D20" t="str">
-        <v>storage(存储)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>plus</v>
       </c>
       <c r="B21" t="str">
-        <v>plus</v>
+        <v>/plʌs/</v>
       </c>
       <c r="C21" t="str">
+        <v>adj./prep.</v>
+      </c>
+      <c r="D21" t="str">
         <v>加上</v>
       </c>
-      <c r="D21" t="str">
-        <v>plus(加上)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>giant</v>
       </c>
       <c r="B22" t="str">
-        <v>giant</v>
+        <v>/ˈdʒaɪənt/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>巨人</v>
       </c>
-      <c r="D22" t="str">
-        <v>giant(巨人)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>technical</v>
       </c>
       <c r="B23" t="str">
-        <v>technical</v>
+        <v>/ˈteknɪkl/</v>
       </c>
       <c r="C23" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>技术上的</v>
       </c>
-      <c r="D23" t="str">
-        <v>technical(技术上的)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>sophisticated</v>
       </c>
       <c r="B24" t="str">
-        <v>sophisticated</v>
+        <v>/səˈfɪstɪkeɪtɪd/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>精致的</v>
       </c>
-      <c r="D24" t="str">
-        <v>sophisticated(精致的)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>hundred</v>
       </c>
       <c r="B25" t="str">
-        <v>hundred</v>
+        <v>/ˈhʌndrəd/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D25" t="str">
         <v>一百</v>
       </c>
-      <c r="D25" t="str">
-        <v>hundred(一百)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>glide</v>
       </c>
       <c r="B26" t="str">
-        <v>glide</v>
+        <v>/ɡlaɪd/</v>
       </c>
       <c r="C26" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D26" t="str">
         <v>滑行</v>
       </c>
-      <c r="D26" t="str">
-        <v>glide(滑行)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>vanity</v>
       </c>
       <c r="B27" t="str">
-        <v>vanity</v>
+        <v>/ˈvænəti/</v>
       </c>
       <c r="C27" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>虚荣心</v>
       </c>
-      <c r="D27" t="str">
-        <v>vanity(虚荣心)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>supper</v>
       </c>
       <c r="B28" t="str">
-        <v>supper</v>
+        <v>/ˈsʌpər/</v>
       </c>
       <c r="C28" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>晚餐</v>
       </c>
-      <c r="D28" t="str">
-        <v>supper(晚餐)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>jam</v>
       </c>
       <c r="B29" t="str">
-        <v>jam</v>
+        <v>/dʒæm/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D29" t="str">
         <v>果酱</v>
       </c>
-      <c r="D29" t="str">
-        <v>jam(果酱)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>birthday</v>
       </c>
       <c r="B30" t="str">
-        <v>birthday</v>
+        <v>/ˈbɜːrθdeɪ/</v>
       </c>
       <c r="C30" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>生日</v>
       </c>
-      <c r="D30" t="str">
-        <v>birthday(生日)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>ring</v>
       </c>
       <c r="B31" t="str">
-        <v>ring</v>
+        <v>/rɪŋ/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D31" t="str">
         <v>戒指</v>
       </c>
-      <c r="D31" t="str">
-        <v>ring(戒指)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>direct</v>
       </c>
       <c r="B32" t="str">
-        <v>direct</v>
+        <v>/dəˈrekt,daɪˈrekt/</v>
       </c>
       <c r="C32" t="str">
+        <v>vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D32" t="str">
         <v>直接的</v>
       </c>
-      <c r="D32" t="str">
-        <v>direct(直接的)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>contradiction</v>
       </c>
       <c r="B33" t="str">
-        <v>contradiction</v>
+        <v>/ˌkɑːntrəˈdɪkʃn/</v>
       </c>
       <c r="C33" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>矛盾</v>
       </c>
-      <c r="D33" t="str">
-        <v>contradiction(矛盾)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>prejudice</v>
       </c>
       <c r="B34" t="str">
-        <v>prejudice</v>
+        <v>/ˈpredʒudɪs/</v>
       </c>
       <c r="C34" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D34" t="str">
         <v>偏见</v>
       </c>
-      <c r="D34" t="str">
-        <v>prejudice(偏见)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>spelling</v>
       </c>
       <c r="B35" t="str">
-        <v>spelling</v>
+        <v>/ˈspelɪŋ/</v>
       </c>
       <c r="C35" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D35" t="str">
         <v>拼写</v>
       </c>
-      <c r="D35" t="str">
-        <v>spelling(拼写)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>cheer</v>
       </c>
       <c r="B36" t="str">
-        <v>cheer</v>
+        <v>/tʃɪr/</v>
       </c>
       <c r="C36" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D36" t="str">
         <v>欢呼</v>
       </c>
-      <c r="D36" t="str">
-        <v>cheer(欢呼)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>predict</v>
       </c>
       <c r="B37" t="str">
-        <v>predict</v>
+        <v>/prɪˈdɪkt/</v>
       </c>
       <c r="C37" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D37" t="str">
         <v>预言</v>
       </c>
-      <c r="D37" t="str">
-        <v>predict(预言)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>rival</v>
       </c>
       <c r="B38" t="str">
-        <v>rival</v>
+        <v>/ˈraɪvl/</v>
       </c>
       <c r="C38" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D38" t="str">
         <v>竞争对手</v>
       </c>
-      <c r="D38" t="str">
-        <v>rival(竞争对手)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>spot</v>
       </c>
       <c r="B39" t="str">
-        <v>spot</v>
+        <v>/spɑːt/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D39" t="str">
         <v>地点</v>
       </c>
-      <c r="D39" t="str">
-        <v>spot(地点)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>clothes</v>
       </c>
       <c r="B40" t="str">
-        <v>clothes</v>
+        <v>/kloʊðz,kloʊz/</v>
       </c>
       <c r="C40" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>衣服</v>
       </c>
-      <c r="D40" t="str">
-        <v>clothes(衣服)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>grave</v>
       </c>
       <c r="B41" t="str">
-        <v>grave</v>
+        <v>/ɡreɪv; ɡrɑːv/</v>
       </c>
       <c r="C41" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D41" t="str">
         <v>严重</v>
       </c>
-      <c r="D41" t="str">
-        <v>grave(严重)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>pick</v>
       </c>
       <c r="B42" t="str">
-        <v>pick</v>
+        <v>/pɪk/</v>
       </c>
       <c r="C42" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D42" t="str">
         <v>挑选</v>
       </c>
-      <c r="D42" t="str">
-        <v>pick(挑选)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>oppress</v>
       </c>
       <c r="B43" t="str">
-        <v>oppress</v>
+        <v>/əˈpres/</v>
       </c>
       <c r="C43" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D43" t="str">
         <v>压迫</v>
       </c>
-      <c r="D43" t="str">
-        <v>oppress(压迫)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>call</v>
       </c>
       <c r="B44" t="str">
-        <v>call</v>
+        <v>/kɔːl/</v>
       </c>
       <c r="C44" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D44" t="str">
         <v>呼叫</v>
       </c>
-      <c r="D44" t="str">
-        <v>call(呼叫)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>brute</v>
       </c>
       <c r="B45" t="str">
-        <v>brute</v>
+        <v>/bruːt/</v>
       </c>
       <c r="C45" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D45" t="str">
         <v>残忍的</v>
       </c>
-      <c r="D45" t="str">
-        <v>brute(残忍的)📢</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>those</v>
       </c>
       <c r="B46" t="str">
-        <v>those</v>
+        <v>/ðoʊz/</v>
       </c>
       <c r="C46" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D46" t="str">
         <v>那些</v>
       </c>
-      <c r="D46" t="str">
-        <v>those(那些)📢</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>collection</v>
       </c>
       <c r="B47" t="str">
-        <v>collection</v>
+        <v>/kəˈlekʃn/</v>
       </c>
       <c r="C47" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>收藏品</v>
       </c>
-      <c r="D47" t="str">
-        <v>collection(收藏品)📢</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>fade</v>
       </c>
       <c r="B48" t="str">
-        <v>fade</v>
+        <v>/feɪd/</v>
       </c>
       <c r="C48" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D48" t="str">
         <v>消失</v>
       </c>
-      <c r="D48" t="str">
-        <v>fade(消失)📢</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>soil</v>
       </c>
       <c r="B49" t="str">
-        <v>soil</v>
+        <v>/sɔɪl/</v>
       </c>
       <c r="C49" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D49" t="str">
         <v>土地</v>
       </c>
-      <c r="D49" t="str">
-        <v>soil(土地)📢</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>annual</v>
       </c>
       <c r="B50" t="str">
-        <v>annual</v>
+        <v>/ˈænjuəl/</v>
       </c>
       <c r="C50" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D50" t="str">
         <v>年度</v>
       </c>
-      <c r="D50" t="str">
-        <v>annual(年度)📢</v>
-      </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>conduct</v>
       </c>
       <c r="B51" t="str">
-        <v>conduct</v>
+        <v>/kənˈdʌkt/</v>
       </c>
       <c r="C51" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D51" t="str">
         <v>行为</v>
-      </c>
-      <c r="D51" t="str">
-        <v>conduct(行为)📢</v>
       </c>
     </row>
   </sheetData>
